--- a/pensum/ok03/LOM_Ovingsark_Okonomistyring_kap03_Resultat_og_balanse_NY.xlsx
+++ b/pensum/ok03/LOM_Ovingsark_Okonomistyring_kap03_Resultat_og_balanse_NY.xlsx
@@ -606,6 +606,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
@@ -685,6 +686,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
@@ -720,6 +722,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
@@ -734,6 +737,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
@@ -775,6 +779,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
@@ -935,6 +940,7 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
@@ -963,6 +969,7 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
@@ -977,6 +984,7 @@
         </is>
       </c>
     </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
@@ -1008,7 +1016,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Nordlys Elektro AS er en konstruert casebedrift. Tallene henger sammen på tvers av alle ti kapitlene i Bok 1.</t>
+          <t>Nordlys Elektro AS er en konstruert casebedrift. Tallene henger sammen på tvers av alle ti kapitlene i Økonomistyring for LØM-emnet.</t>
         </is>
       </c>
     </row>
@@ -1048,6 +1056,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -1111,11 +1120,11 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Varekostnad, underentreprenør</t>
+          <t>Varekostnad, innleide montører</t>
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>3660000</v>
+        <v>400000</v>
       </c>
       <c r="C7" s="11">
         <f>B7/$B$5</f>
@@ -1154,7 +1163,7 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>7400000</v>
+        <v>10660000</v>
       </c>
       <c r="C9" s="11">
         <f>B9/$B$5</f>
@@ -1341,6 +1350,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
@@ -1401,6 +1411,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
@@ -1448,6 +1459,7 @@
         <v/>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
@@ -1479,7 +1491,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Kilde: oppstillingen følger Bok 1 kap. 3.3. Tallene er Nordlys Elektro AS 2026.</t>
+          <t>Kilde: oppstillingen følger Økonomistyring for LØM-emnet, kap. 3.3. Tallene er Nordlys Elektro AS 2026.</t>
         </is>
       </c>
     </row>
@@ -1536,6 +1548,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -1626,6 +1639,7 @@
         <v/>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -1770,6 +1784,7 @@
         <v/>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
@@ -1790,6 +1805,7 @@
         <v/>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
@@ -1819,6 +1835,7 @@
         <v/>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
@@ -1908,6 +1925,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
@@ -1931,6 +1949,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
@@ -1969,6 +1988,7 @@
         <v/>
       </c>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
@@ -1979,7 +1999,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Kilde: oppstillingen følger Bok 1 kap. 3.2. Tallene er Nordlys Elektro AS.</t>
+          <t>Kilde: oppstillingen følger Økonomistyring for LØM-emnet, kap. 3.2. Tallene er Nordlys Elektro AS.</t>
         </is>
       </c>
     </row>
@@ -2036,6 +2056,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2073,6 +2094,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
@@ -2209,6 +2231,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
@@ -2254,6 +2277,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
@@ -2283,6 +2307,7 @@
         <v/>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
@@ -2422,6 +2447,7 @@
         <v/>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
@@ -2432,7 +2458,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Kilde: Bok 1 kap. 3.2. Aktiveringsgrensene følger skatteloven § 14-40 (Lovdata): kostpris minst 30 000 kroner OG økonomisk levetid minst 3 år. Oppstillingsplanene følger regnskapsloven kapittel 6 (Lovdata).</t>
+          <t>Kilde: Økonomistyring for LØM-emnet, kap. 3.2. Aktiveringsgrensene følger skatteloven § 14-40 (Lovdata): kostpris minst 30 000 kroner OG økonomisk levetid minst 3 år. Oppstillingsplanene følger regnskapsloven kapittel 6 (Lovdata).</t>
         </is>
       </c>
     </row>
@@ -2483,6 +2509,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2587,6 +2614,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
@@ -2713,6 +2741,7 @@
         <v/>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
@@ -2800,6 +2829,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
@@ -2840,6 +2870,7 @@
         <v/>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
@@ -2857,7 +2888,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Kilde: Bok 1 kap. 3.2 og kap. 4.2. Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent.</t>
+          <t>Kilde: Økonomistyring for LØM-emnet, kap. 3.2 og kap. 4.2. Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent.</t>
         </is>
       </c>
     </row>
@@ -2914,6 +2945,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -2934,6 +2966,7 @@
         <v>2026</v>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
@@ -3204,6 +3237,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
@@ -3281,6 +3315,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
@@ -3321,6 +3356,7 @@
         <v/>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
@@ -3380,6 +3416,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3394,6 +3431,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
@@ -3474,6 +3512,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
@@ -3539,6 +3578,7 @@
         <v/>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
@@ -3584,6 +3624,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
@@ -3620,6 +3661,8 @@
         <v/>
       </c>
     </row>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
@@ -3634,6 +3677,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
@@ -3697,6 +3741,7 @@
         <v/>
       </c>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
@@ -3780,6 +3825,7 @@
         <v/>
       </c>
     </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
@@ -3836,6 +3882,7 @@
         </is>
       </c>
     </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
@@ -3924,6 +3971,7 @@
         <v/>
       </c>
     </row>
+    <row r="63"/>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
@@ -3982,10 +4030,11 @@
         <v/>
       </c>
     </row>
+    <row r="70"/>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>Kilde: Bok 1 kap. 3.2 og 3.3, med støtte i kap. 4 om nøkkeltall og kap. 9 om likviditetsbudsjett. Normtallene for likviditetsgrad står i Bok 1 kap. 4.2.2. Rammen og søknadsbeløpet er konstruert for øvingen.</t>
+          <t>Kilde: Økonomistyring for LØM-emnet, kap. 3.2 og 3.3, med støtte i kap. 4 om nøkkeltall og kap. 9 om likviditetsbudsjett. Normtallene for likviditetsgrad står i Økonomistyring for LØM-emnet, kap. 4.2.2. Rammen og søknadsbeløpet er konstruert for øvingen.</t>
         </is>
       </c>
     </row>
